--- a/data/ov.xlsx
+++ b/data/ov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E7CA08-E3FE-EE44-8AA0-41194B735625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C20C898-158C-7246-AC9D-C6C48126ED9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="20" r:id="rId1"/>
     <sheet name="Onderwerp" sheetId="10" r:id="rId2"/>
-    <sheet name="CombLeerdoelOpleidingsniveau" sheetId="19" r:id="rId3"/>
+    <sheet name="DoelCollectie" sheetId="19" r:id="rId3"/>
     <sheet name="Doel" sheetId="21" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -31,14 +31,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="405">
   <si>
     <t>CODE</t>
   </si>
   <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -537,18 +534,6 @@
     <t>L-lj5 | L-lj6</t>
   </si>
   <si>
-    <t>leerplan</t>
-  </si>
-  <si>
-    <t>versieDatum</t>
-  </si>
-  <si>
-    <t>collectiedoel</t>
-  </si>
-  <si>
-    <t>collectiedoeltype</t>
-  </si>
-  <si>
     <t>OV</t>
   </si>
   <si>
@@ -870,18 +855,12 @@
     <t>S-gr3-DoF | S-gr3-DuF</t>
   </si>
   <si>
-    <t>Doeltype</t>
-  </si>
-  <si>
     <t>Basiscompetentie</t>
   </si>
   <si>
     <t>Beroepskwalificatie</t>
   </si>
   <si>
-    <t>V2_1</t>
-  </si>
-  <si>
     <t>Cesuurdoel</t>
   </si>
   <si>
@@ -1266,7 +1245,7 @@
     <t>De leerlingen analyseren de wisselwerking tussen wetenschappen, technologie, wiskunde en de maatschappij aan de hand van maatschappelijke uitdagingen.</t>
   </si>
   <si>
-    <t>eigenCombinatieLeerdoelOpleidingsniveau</t>
+    <t>isLidVan</t>
   </si>
 </sst>
 </file>
@@ -1734,15 +1713,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1764,1059 +1743,1059 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E54" s="4"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E56" s="4"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E58" s="4"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2827,865 +2806,677 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0786D6D-46BC-484B-A8CE-DF03180E4E7E}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="40" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="B4" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C7" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="E7" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="H2" s="4" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H3" s="5" t="s">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H4" s="4" t="s">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H5" s="5" t="s">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H6" s="4" t="s">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F7" s="5" t="s">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F8" s="4" t="s">
+    </row>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="5" t="s">
+    </row>
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>284</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3715,7 +3506,7 @@
     <col min="14" max="14" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -3723,1112 +3514,1112 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q45" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q49" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q51" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q53" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/data/ov.xlsx
+++ b/data/ov.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C20C898-158C-7246-AC9D-C6C48126ED9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73964203-DDE8-4348-BDD1-4D6C1606F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="20" r:id="rId1"/>
-    <sheet name="Onderwerp" sheetId="10" r:id="rId2"/>
+    <sheet name="OnderwerpType" sheetId="10" r:id="rId2"/>
     <sheet name="DoelCollectie" sheetId="19" r:id="rId3"/>
     <sheet name="Doel" sheetId="21" r:id="rId4"/>
+    <sheet name="_customVoc" sheetId="22" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="418">
   <si>
     <t>CODE</t>
   </si>
@@ -1246,13 +1247,52 @@
   </si>
   <si>
     <t>isLidVan</t>
+  </si>
+  <si>
+    <t>sheetLabel</t>
+  </si>
+  <si>
+    <t>OnderwerpType</t>
+  </si>
+  <si>
+    <t>sheetClass</t>
+  </si>
+  <si>
+    <t>columnLabel</t>
+  </si>
+  <si>
+    <t>columnProperty</t>
+  </si>
+  <si>
+    <t>valueDatatype</t>
+  </si>
+  <si>
+    <t>valueClass</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#altLabel</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#string</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#Concept</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/educationLevel</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/title</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1266,6 +1306,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1333,10 +1389,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1363,8 +1420,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4626,4 +4686,124 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A62FA0F-B258-B142-9AF9-EA0CF34C792A}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" location="altLabel" xr:uid="{48DAFF21-1FE8-6A40-AE3A-1E4C01A6F0AE}"/>
+    <hyperlink ref="E2" r:id="rId2" location="string" xr:uid="{C45A0868-878A-6344-B4C3-407852F94DED}"/>
+    <hyperlink ref="B2" r:id="rId3" location="Concept" xr:uid="{7C5B7389-5BB3-3947-9976-70E20297D35A}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{E2ABFBE6-8E10-C446-A25F-D39B9C098B8F}"/>
+    <hyperlink ref="B3" r:id="rId5" location="Concept" xr:uid="{22D506F5-FD58-0A40-B48A-404E00477007}"/>
+    <hyperlink ref="F3" r:id="rId6" location="Concept" xr:uid="{702F8F58-1C54-3E4F-A0D5-8CF96214D936}"/>
+    <hyperlink ref="D4" r:id="rId7" xr:uid="{7EF690D0-9C85-D442-9186-604DBC4E7760}"/>
+    <hyperlink ref="D5" r:id="rId8" xr:uid="{979793F4-27B3-C44E-AD74-941A3D860FFF}"/>
+    <hyperlink ref="E4" r:id="rId9" location="string" xr:uid="{2D577B7C-0521-EA43-BF79-9D76C16BC48B}"/>
+    <hyperlink ref="F5" r:id="rId10" location="Concept" xr:uid="{98AEB01A-B756-8D46-BCF3-DF4FF8DAEFE6}"/>
+    <hyperlink ref="B4" r:id="rId11" location="Concept" xr:uid="{A49D8515-1C86-204E-B778-B1676F7CC55D}"/>
+    <hyperlink ref="B5" r:id="rId12" location="Concept" xr:uid="{90DF6829-4686-E940-A4F3-1EDDB4967927}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/ov.xlsx
+++ b/data/ov.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73964203-DDE8-4348-BDD1-4D6C1606F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9895C75-259A-1041-B03D-8ABD873D217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="20" r:id="rId1"/>
@@ -925,9 +925,6 @@
     <t>bestaatUit</t>
   </si>
   <si>
-    <t>hetzelfde</t>
-  </si>
-  <si>
     <t>06.01</t>
   </si>
   <si>
@@ -1286,6 +1283,9 @@
   </si>
   <si>
     <t>http://purl.org/dc/terms/type</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
   </si>
 </sst>
 </file>
@@ -3565,7 +3565,7 @@
     <col min="13" max="13" width="14.5" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3616,21 +3616,21 @@
         <v>296</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>297</v>
+        <v>417</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>167</v>
@@ -3644,13 +3644,13 @@
     </row>
     <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>167</v>
@@ -3664,13 +3664,13 @@
     </row>
     <row r="4" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>167</v>
@@ -3684,13 +3684,13 @@
     </row>
     <row r="5" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>167</v>
@@ -3704,13 +3704,13 @@
     </row>
     <row r="6" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>167</v>
@@ -3724,13 +3724,13 @@
     </row>
     <row r="7" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>167</v>
@@ -3744,13 +3744,13 @@
     </row>
     <row r="8" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>167</v>
@@ -3764,13 +3764,13 @@
     </row>
     <row r="9" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>167</v>
@@ -3784,13 +3784,13 @@
     </row>
     <row r="10" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>167</v>
@@ -3804,13 +3804,13 @@
     </row>
     <row r="11" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>167</v>
@@ -3824,13 +3824,13 @@
     </row>
     <row r="12" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>167</v>
@@ -3844,13 +3844,13 @@
     </row>
     <row r="13" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>167</v>
@@ -3864,13 +3864,13 @@
     </row>
     <row r="14" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>167</v>
@@ -3884,13 +3884,13 @@
     </row>
     <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>167</v>
@@ -3904,13 +3904,13 @@
     </row>
     <row r="16" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>167</v>
@@ -3924,13 +3924,13 @@
     </row>
     <row r="17" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>167</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>167</v>
@@ -3964,13 +3964,13 @@
     </row>
     <row r="19" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>167</v>
@@ -3984,13 +3984,13 @@
     </row>
     <row r="20" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>167</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="21" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>167</v>
@@ -4024,13 +4024,13 @@
     </row>
     <row r="22" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>167</v>
@@ -4044,13 +4044,13 @@
     </row>
     <row r="23" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>167</v>
@@ -4064,13 +4064,13 @@
     </row>
     <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>167</v>
@@ -4084,13 +4084,13 @@
     </row>
     <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>167</v>
@@ -4104,13 +4104,13 @@
     </row>
     <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>167</v>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="27" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>167</v>
@@ -4144,13 +4144,13 @@
     </row>
     <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>167</v>
@@ -4164,13 +4164,13 @@
     </row>
     <row r="29" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>167</v>
@@ -4184,13 +4184,13 @@
     </row>
     <row r="30" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>167</v>
@@ -4204,13 +4204,13 @@
     </row>
     <row r="31" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>167</v>
@@ -4224,13 +4224,13 @@
     </row>
     <row r="32" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>167</v>
@@ -4244,13 +4244,13 @@
     </row>
     <row r="33" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>167</v>
@@ -4264,13 +4264,13 @@
     </row>
     <row r="34" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>167</v>
@@ -4284,13 +4284,13 @@
     </row>
     <row r="35" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>167</v>
@@ -4304,13 +4304,13 @@
     </row>
     <row r="36" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>167</v>
@@ -4324,13 +4324,13 @@
     </row>
     <row r="37" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>167</v>
@@ -4344,13 +4344,13 @@
     </row>
     <row r="38" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>167</v>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="39" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>167</v>
@@ -4384,13 +4384,13 @@
     </row>
     <row r="40" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>167</v>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="41" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>167</v>
@@ -4424,13 +4424,13 @@
     </row>
     <row r="42" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>167</v>
@@ -4444,13 +4444,13 @@
     </row>
     <row r="43" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>167</v>
@@ -4464,13 +4464,13 @@
     </row>
     <row r="44" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>167</v>
@@ -4484,13 +4484,13 @@
     </row>
     <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>167</v>
@@ -4504,13 +4504,13 @@
     </row>
     <row r="46" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>167</v>
@@ -4524,13 +4524,13 @@
     </row>
     <row r="47" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>167</v>
@@ -4544,13 +4544,13 @@
     </row>
     <row r="48" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>167</v>
@@ -4564,13 +4564,13 @@
     </row>
     <row r="49" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>167</v>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="50" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>167</v>
@@ -4604,13 +4604,13 @@
     </row>
     <row r="51" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>167</v>
@@ -4624,13 +4624,13 @@
     </row>
     <row r="52" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>167</v>
@@ -4644,13 +4644,13 @@
     </row>
     <row r="53" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>167</v>
@@ -4664,13 +4664,13 @@
     </row>
     <row r="54" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>167</v>
@@ -4702,91 +4702,91 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>410</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>412</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/data/ov.xlsx
+++ b/data/ov.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9895C75-259A-1041-B03D-8ABD873D217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42392100-7DD4-FF4D-A97B-A6EF645AE422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="20" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="420">
   <si>
     <t>CODE</t>
   </si>
@@ -1286,6 +1286,12 @@
   </si>
   <si>
     <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/Agent</t>
   </si>
 </sst>
 </file>
@@ -4690,7 +4696,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A62FA0F-B258-B142-9AF9-EA0CF34C792A}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -4787,6 +4793,23 @@
       </c>
       <c r="F5" s="13" t="s">
         <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -4803,6 +4826,9 @@
     <hyperlink ref="F5" r:id="rId10" location="Concept" xr:uid="{98AEB01A-B756-8D46-BCF3-DF4FF8DAEFE6}"/>
     <hyperlink ref="B4" r:id="rId11" location="Concept" xr:uid="{A49D8515-1C86-204E-B778-B1676F7CC55D}"/>
     <hyperlink ref="B5" r:id="rId12" location="Concept" xr:uid="{90DF6829-4686-E940-A4F3-1EDDB4967927}"/>
+    <hyperlink ref="B6" r:id="rId13" xr:uid="{FA805D05-28B6-6846-916F-BC4CA46A75E9}"/>
+    <hyperlink ref="D6" r:id="rId14" xr:uid="{F7F02DAC-5027-C944-BDC0-C0481F85CA8A}"/>
+    <hyperlink ref="E6" r:id="rId15" location="string" xr:uid="{981C665B-7403-F448-9368-3ABC57FD90E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
